--- a/data/trans_bre/P68-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P68-Clase-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 10,4</t>
+          <t>-3,0; 10,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 12,22</t>
+          <t>-3,02; 12,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 12,35</t>
+          <t>-2,34; 12,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 11,41</t>
+          <t>0,37; 11,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 68,37</t>
+          <t>-15,08; 67,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 79,78</t>
+          <t>-15,03; 76,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 87,99</t>
+          <t>-13,16; 85,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 110,47</t>
+          <t>-0,45; 108,39</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 8,74</t>
+          <t>-5,06; 9,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 9,66</t>
+          <t>-5,48; 9,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 9,68</t>
+          <t>-3,53; 9,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 6,48</t>
+          <t>-6,2; 6,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,77; 71,05</t>
+          <t>-25,87; 72,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,21; 85,51</t>
+          <t>-32,81; 80,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-24,69; 103,56</t>
+          <t>-23,32; 101,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,85; 49,96</t>
+          <t>-32,07; 48,14</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 14,57</t>
+          <t>-10,43; 16,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 12,76</t>
+          <t>-8,5; 12,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,81; -5,4</t>
+          <t>-26,8; -5,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 29,67</t>
+          <t>-1,61; 30,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-36,27; 60,55</t>
+          <t>-36,57; 67,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,01; 50,62</t>
+          <t>-27,45; 47,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-77,33; -17,92</t>
+          <t>-79,0; -16,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 699,26</t>
+          <t>-11,68; 614,57</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,58; -6,57</t>
+          <t>-17,79; -6,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 1,99</t>
+          <t>-12,18; 1,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 0,63</t>
+          <t>-11,34; 0,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 6,39</t>
+          <t>-4,3; 6,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,89; -25,07</t>
+          <t>-57,7; -24,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,7; 7,84</t>
+          <t>-39,46; 6,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 3,05</t>
+          <t>-36,52; 1,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 31,05</t>
+          <t>-16,31; 31,44</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 7,12</t>
+          <t>-12,98; 6,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 8,98</t>
+          <t>-10,72; 8,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,4; -2,1</t>
+          <t>-20,66; -2,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 30,38</t>
+          <t>-4,04; 29,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-34,41; 24,44</t>
+          <t>-32,52; 22,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 44,79</t>
+          <t>-34,36; 42,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-50,95; -6,93</t>
+          <t>-51,44; -9,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 155,07</t>
+          <t>-14,98; 162,18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1112,42 +1112,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3,44</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,61</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3,84</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,03</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-13,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-2,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-15,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,66%</t>
         </is>
       </c>
     </row>
@@ -1160,160 +1160,59 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,36; -0,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,03; 2,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,2; -0,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,34; 16,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-24,04; -0,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-15,99; 13,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-27,35; -2,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,88; 111,76</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-3,44</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,61</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,84</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,03</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-13,77%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-2,63%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-15,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>39,66%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-6,43; 0,34</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-4,3; 2,94</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-7,28; -0,09</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1,91; 15,02</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-24,88; 1,73</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-17,41; 12,92</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-27,43; -0,33</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>9,8; 115,88</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>

--- a/data/trans_bre/P68-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P68-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>4,58</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 10,72</t>
+          <t>-3,34; 9,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 12,12</t>
+          <t>-3,12; 12,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 12,25</t>
+          <t>-2,78; 12,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 11,27</t>
+          <t>-0,84; 9,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 67,28</t>
+          <t>-18,02; 64,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 76,28</t>
+          <t>-15,26; 84,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 85,57</t>
+          <t>-15,05; 95,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 108,39</t>
+          <t>-6,81; 87,33</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 9,12</t>
+          <t>-4,56; 9,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 9,63</t>
+          <t>-5,55; 10,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 9,55</t>
+          <t>-3,37; 10,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 6,64</t>
+          <t>-6,47; 6,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 72,31</t>
+          <t>-23,86; 74,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,81; 80,91</t>
+          <t>-35,06; 98,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,32; 101,38</t>
+          <t>-23,44; 104,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 48,14</t>
+          <t>-30,69; 47,17</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,87</t>
+          <t>2,45</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>107,16%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 16,38</t>
+          <t>-9,73; 15,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 12,1</t>
+          <t>-8,58; 12,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,8; -5,37</t>
+          <t>-26,3; -5,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 30,86</t>
+          <t>-7,56; 12,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-36,57; 67,94</t>
+          <t>-35,28; 62,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,45; 47,66</t>
+          <t>-28,31; 47,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-79,0; -16,65</t>
+          <t>-77,62; -17,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 614,57</t>
+          <t>-28,81; 61,26</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>-0,99</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>-3,96%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,79; -6,86</t>
+          <t>-17,42; -6,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 1,58</t>
+          <t>-11,57; 1,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 0,31</t>
+          <t>-11,7; 0,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 6,56</t>
+          <t>-6,54; 3,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,7; -24,93</t>
+          <t>-56,51; -25,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,46; 6,62</t>
+          <t>-37,73; 6,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,52; 1,44</t>
+          <t>-37,23; 2,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 31,44</t>
+          <t>-22,97; 17,23</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,64</t>
+          <t>11,4</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>52,57%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 6,47</t>
+          <t>-13,8; 6,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 8,6</t>
+          <t>-11,08; 8,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,66; -2,67</t>
+          <t>-20,48; -1,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 29,65</t>
+          <t>4,97; 18,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,52; 22,68</t>
+          <t>-34,19; 20,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,36; 42,52</t>
+          <t>-35,85; 38,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-51,44; -9,02</t>
+          <t>-50,72; -5,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 162,18</t>
+          <t>18,66; 101,01</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,03</t>
+          <t>2,91</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,36; -0,09</t>
+          <t>-6,96; 0,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 2,82</t>
+          <t>-3,79; 3,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,2; -0,48</t>
+          <t>-7,22; -0,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,34; 16,62</t>
+          <t>0,06; 5,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,04; -0,22</t>
+          <t>-26,72; 0,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 13,2</t>
+          <t>-15,53; 15,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,35; -2,03</t>
+          <t>-27,29; -0,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,88; 111,76</t>
+          <t>0,41; 30,29</t>
         </is>
       </c>
     </row>
